--- a/model_output/supp/supplemental_bundle.xlsx
+++ b/model_output/supp/supplemental_bundle.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t xml:space="preserve">Term</t>
   </si>
@@ -51,25 +51,25 @@
     <t xml:space="preserve">ent_typeFacial Plastics</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696</t>
+    <t xml:space="preserve">0.706</t>
   </si>
   <si>
     <t xml:space="preserve">ent_typeHead and Neck Cancer</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661</t>
+    <t xml:space="preserve">0.669</t>
   </si>
   <si>
     <t xml:space="preserve">ent_typeLaryngology</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385</t>
+    <t xml:space="preserve">0.386</t>
   </si>
   <si>
     <t xml:space="preserve">ent_typeOtology/neurotology</t>
   </si>
   <si>
-    <t xml:space="preserve">0.074</t>
+    <t xml:space="preserve">0.072</t>
   </si>
   <si>
     <t xml:space="preserve">ent_typePediatrics</t>
@@ -87,19 +87,19 @@
     <t xml:space="preserve">ent_typeSleep</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371</t>
+    <t xml:space="preserve">0.373</t>
   </si>
   <si>
     <t xml:space="preserve">ent_per_100k_z</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603</t>
+    <t xml:space="preserve">0.552</t>
   </si>
   <si>
     <t xml:space="preserve">medicaid_fee_index_z</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250</t>
+    <t xml:space="preserve">0.254</t>
   </si>
   <si>
     <t xml:space="preserve">svi_overall_z</t>
@@ -111,19 +111,13 @@
     <t xml:space="preserve">dual_pct_z</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975</t>
+    <t xml:space="preserve">0.958</t>
   </si>
   <si>
     <t xml:space="preserve">ruralRural</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ruralSuburban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857</t>
+    <t xml:space="preserve">0.922</t>
   </si>
   <si>
     <t xml:space="preserve">caller_fDeol</t>
@@ -171,58 +165,58 @@
     <t xml:space="preserve">&lt;0.001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421</t>
+    <t xml:space="preserve">0.856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423</t>
   </si>
   <si>
     <t xml:space="preserve">0.020</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557</t>
+    <t xml:space="preserve">0.562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.032</t>
   </si>
   <si>
     <t xml:space="preserve">0.121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379</t>
+    <t xml:space="preserve">0.647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377</t>
   </si>
   <si>
     <t xml:space="preserve">Model</t>
@@ -282,13 +276,13 @@
     <t xml:space="preserve">Date created</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-14 23:36:17 MDT</t>
+    <t xml:space="preserve">2026-07-15 20:53:40 MDT</t>
   </si>
   <si>
     <t xml:space="preserve">Package: mysterycall</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6.0.9001</t>
+    <t xml:space="preserve">1.6.0.9006</t>
   </si>
   <si>
     <t xml:space="preserve">Package: openxlsx</t>
@@ -754,7 +748,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.2046</v>
+        <v>-0.2048</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.1892</v>
@@ -780,22 +774,22 @@
         <v>10</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>-0.104</v>
+        <v>-0.1004</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.2658</v>
+        <v>0.2656</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>-0.391</v>
+        <v>-0.378</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0.901</v>
+        <v>0.905</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.535</v>
+        <v>0.537</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.518</v>
+        <v>1.522</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>11</v>
@@ -806,22 +800,22 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1864</v>
+        <v>-0.1818</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.4257</v>
+        <v>0.4256</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.438</v>
+        <v>-0.427</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.83</v>
+        <v>0.834</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.36</v>
+        <v>0.362</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.912</v>
+        <v>1.92</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>13</v>
@@ -832,22 +826,22 @@
         <v>14</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.5547</v>
+        <v>0.5528</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.6382</v>
+        <v>0.6381</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.869</v>
+        <v>0.866</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1.741</v>
+        <v>1.738</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6.083</v>
+        <v>6.071</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>15</v>
@@ -858,22 +852,22 @@
         <v>16</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-0.7041</v>
+        <v>-0.709</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.3947</v>
+        <v>0.3945</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-1.784</v>
+        <v>-1.797</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.495</v>
+        <v>0.492</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.228</v>
+        <v>0.227</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.072</v>
+        <v>1.066</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>17</v>
@@ -884,22 +878,22 @@
         <v>18</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.8153</v>
+        <v>0.8181</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0.3785</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2.154</v>
+        <v>2.162</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2.26</v>
+        <v>2.266</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1.076</v>
+        <v>1.079</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>4.746</v>
+        <v>4.758</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>19</v>
@@ -910,22 +904,22 @@
         <v>20</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.7451</v>
+        <v>0.7463</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.5486</v>
+        <v>0.5489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.358</v>
+        <v>1.36</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2.107</v>
+        <v>2.109</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0.719</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>6.174</v>
+        <v>6.185</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>21</v>
@@ -936,22 +930,22 @@
         <v>22</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.5061</v>
+        <v>0.5042</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.5657</v>
+        <v>0.5654</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.895</v>
+        <v>0.892</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1.659</v>
+        <v>1.656</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0.547</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5.027</v>
+        <v>5.015</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>23</v>
@@ -962,22 +956,22 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-0.044</v>
+        <v>-0.0494</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.0845</v>
+        <v>0.0832</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.594</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.957</v>
+        <v>0.952</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.811</v>
+        <v>0.808</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.129</v>
+        <v>1.12</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>25</v>
@@ -988,13 +982,13 @@
         <v>26</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>-0.0948</v>
+        <v>-0.0941</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>0.0825</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-1.15</v>
+        <v>-1.142</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>0.91</v>
@@ -1003,7 +997,7 @@
         <v>0.774</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1.069</v>
+        <v>1.07</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>27</v>
@@ -1020,7 +1014,7 @@
         <v>0.0889</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.549</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0.952</v>
@@ -1040,22 +1034,22 @@
         <v>30</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-0.0029</v>
+        <v>-0.0049</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.0924</v>
+        <v>0.0923</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.031</v>
+        <v>-0.053</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.997</v>
+        <v>0.995</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.832</v>
+        <v>0.83</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.195</v>
+        <v>1.192</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>31</v>
@@ -1066,22 +1060,22 @@
         <v>32</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-0.0723</v>
+        <v>0.0178</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3223</v>
+        <v>0.1822</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-0.224</v>
+        <v>0.098</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.93</v>
+        <v>1.018</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.495</v>
+        <v>0.712</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1.75</v>
+        <v>1.455</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>33</v>
@@ -1092,22 +1086,22 @@
         <v>34</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.0339</v>
+        <v>0.8494</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.1885</v>
+        <v>0.2547</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.18</v>
+        <v>3.335</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1.034</v>
+        <v>2.338</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.715</v>
+        <v>1.419</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1.497</v>
+        <v>3.852</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>35</v>
@@ -1118,22 +1112,22 @@
         <v>36</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.851</v>
+        <v>0.692</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.2547</v>
+        <v>0.2895</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.341</v>
+        <v>2.391</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.342</v>
+        <v>1.998</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.422</v>
+        <v>1.133</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.858</v>
+        <v>3.523</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>37</v>
@@ -1144,22 +1138,22 @@
         <v>38</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.693</v>
+        <v>0.6378</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.2895</v>
+        <v>0.2543</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2.394</v>
+        <v>2.508</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>2</v>
+        <v>1.892</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1.134</v>
+        <v>1.15</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>3.527</v>
+        <v>3.115</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>39</v>
@@ -1170,22 +1164,22 @@
         <v>40</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.6398</v>
+        <v>0.6849</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.2543</v>
+        <v>0.2545</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2.516</v>
+        <v>2.691</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1.896</v>
+        <v>1.984</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.152</v>
+        <v>1.204</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3.121</v>
+        <v>3.266</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>41</v>
@@ -1196,22 +1190,22 @@
         <v>42</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.6848</v>
+        <v>-0.694</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.2545</v>
+        <v>0.6346</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2.691</v>
+        <v>-1.094</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>1.983</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1.205</v>
+        <v>0.144</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>3.266</v>
+        <v>1.733</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>43</v>
@@ -1222,51 +1216,25 @@
         <v>44</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.6944</v>
+        <v>0.8065</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.6345</v>
+        <v>0.25</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-1.095</v>
+        <v>3.226</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.499</v>
+        <v>2.24</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.144</v>
+        <v>1.372</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.732</v>
+        <v>3.657</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>0.8095</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>0.2502</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>3.235</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>1.376</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>3.669</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1295,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1304,7 +1272,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -1327,19 +1295,19 @@
         <v>0.1537</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>19.551</v>
+        <v>19.545</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>20.17</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>14.925</v>
+        <v>14.923</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>27.258</v>
+        <v>27.261</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -1347,25 +1315,25 @@
         <v>10</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.035</v>
+        <v>0.0341</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.1878</v>
+        <v>0.1877</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.186</v>
+        <v>0.182</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1.036</v>
+        <v>1.035</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.717</v>
+        <v>0.716</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.496</v>
+        <v>1.495</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -1373,25 +1341,25 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.233</v>
+        <v>0.2316</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2893</v>
+        <v>0.2892</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.805</v>
+        <v>0.801</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1.262</v>
+        <v>1.261</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.716</v>
+        <v>0.715</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2.226</v>
+        <v>2.222</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -1399,25 +1367,25 @@
         <v>14</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.8105</v>
+        <v>0.8113</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.3494</v>
+        <v>0.3492</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.32</v>
+        <v>2.323</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>2.249</v>
+        <v>2.251</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1.134</v>
+        <v>1.135</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4.461</v>
+        <v>4.463</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -1425,25 +1393,25 @@
         <v>16</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.1883</v>
+        <v>0.1858</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.3205</v>
+        <v>0.3204</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.587</v>
+        <v>0.58</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1.207</v>
+        <v>1.204</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.644</v>
+        <v>0.643</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2.263</v>
+        <v>2.256</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -1451,25 +1419,25 @@
         <v>18</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.4326</v>
+        <v>0.4297</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.2005</v>
+        <v>0.2002</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2.157</v>
+        <v>2.147</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1.541</v>
+        <v>1.537</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1.04</v>
+        <v>1.038</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2.283</v>
+        <v>2.275</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -1477,25 +1445,25 @@
         <v>20</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.4356</v>
+        <v>0.4351</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.2806</v>
+        <v>0.2805</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.552</v>
+        <v>1.551</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.546</v>
+        <v>1.545</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0.892</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2.679</v>
+        <v>2.678</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1503,25 +1471,25 @@
         <v>22</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.1532</v>
+        <v>0.1525</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.3332</v>
+        <v>0.3334</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1.166</v>
+        <v>1.165</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.607</v>
+        <v>0.606</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>2.239</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -1529,25 +1497,25 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-0.0547</v>
+        <v>-0.0514</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.0809</v>
+        <v>0.08</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.676</v>
+        <v>-0.643</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.947</v>
+        <v>0.95</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.808</v>
+        <v>0.812</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.109</v>
+        <v>1.111</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -1555,13 +1523,13 @@
         <v>26</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>-0.042</v>
+        <v>-0.0423</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.0693</v>
+        <v>0.0694</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-0.606</v>
+        <v>-0.609</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>0.959</v>
@@ -1573,7 +1541,7 @@
         <v>1.098</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -1581,25 +1549,25 @@
         <v>28</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-0.0495</v>
+        <v>-0.0502</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.0618</v>
+        <v>0.0617</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.801</v>
+        <v>-0.813</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.952</v>
+        <v>0.951</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0.843</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.074</v>
+        <v>1.073</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -1607,25 +1575,25 @@
         <v>30</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-0.0171</v>
+        <v>-0.0153</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.068</v>
+        <v>0.0676</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.252</v>
+        <v>-0.227</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.983</v>
+        <v>0.985</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.86</v>
+        <v>0.862</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.123</v>
+        <v>1.124</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -1633,25 +1601,25 @@
         <v>32</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.1314</v>
+        <v>0.0825</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2366</v>
+        <v>0.1375</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.555</v>
+        <v>0.6</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1.14</v>
+        <v>1.086</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.717</v>
+        <v>0.829</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1.813</v>
+        <v>1.422</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -1659,25 +1627,25 @@
         <v>34</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.0732</v>
+        <v>-0.1982</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.1422</v>
+        <v>0.1675</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.515</v>
+        <v>-1.183</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1.076</v>
+        <v>0.82</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.814</v>
+        <v>0.591</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1.422</v>
+        <v>1.139</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1685,25 +1653,25 @@
         <v>36</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.1989</v>
+        <v>-0.491</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.1675</v>
+        <v>0.2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.187</v>
+        <v>-2.455</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.82</v>
+        <v>0.612</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.59</v>
+        <v>0.414</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.138</v>
+        <v>0.906</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -1711,25 +1679,25 @@
         <v>38</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>-0.4888</v>
+        <v>-0.0012</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.2002</v>
+        <v>0.1729</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>-2.442</v>
+        <v>-0.007</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.613</v>
+        <v>0.999</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.414</v>
+        <v>0.712</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.908</v>
+        <v>1.402</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
@@ -1737,25 +1705,25 @@
         <v>40</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.0049</v>
+        <v>0</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.1735</v>
+        <v>0.1777</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-0.028</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.708</v>
+        <v>0.706</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.398</v>
+        <v>1.417</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
@@ -1763,25 +1731,25 @@
         <v>42</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.0003</v>
+        <v>-0.3078</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.1777</v>
+        <v>0.5366</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.002</v>
+        <v>-0.574</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>1</v>
+        <v>0.735</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.706</v>
+        <v>0.257</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1.417</v>
+        <v>2.104</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1789,51 +1757,25 @@
         <v>44</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.309</v>
+        <v>-0.1507</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.5368</v>
+        <v>0.1706</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-0.576</v>
+        <v>-0.883</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.734</v>
+        <v>0.86</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.256</v>
+        <v>0.616</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.103</v>
+        <v>1.202</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>0.1707</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>-0.879</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0.616</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>1.203</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1858,36 +1800,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>991.17</v>
+        <v>989.28</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1087.65</v>
+        <v>1081.17</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>731</v>
@@ -1904,13 +1846,13 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>3572.57</v>
+        <v>3570.64</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>3661.98</v>
+        <v>3655.98</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>430</v>
@@ -1919,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2581.4</v>
+        <v>2581.36</v>
       </c>
       <c r="G3" s="7" t="b">
         <v>0</v>
@@ -1945,24 +1887,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>731</v>
@@ -1979,7 +1921,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>430</v>
@@ -2011,90 +1953,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/model_output/supp/supplemental_bundle.xlsx
+++ b/model_output/supp/supplemental_bundle.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t xml:space="preserve">Term</t>
   </si>
@@ -165,58 +165,55 @@
     <t xml:space="preserve">&lt;0.001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423</t>
+    <t xml:space="preserve">0.724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364</t>
   </si>
   <si>
     <t xml:space="preserve">0.020</t>
   </si>
   <si>
-    <t xml:space="preserve">0.562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.237</t>
+    <t xml:space="preserve">0.013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.225</t>
   </si>
   <si>
     <t xml:space="preserve">0.014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377</t>
+    <t xml:space="preserve">0.528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456</t>
   </si>
   <si>
     <t xml:space="preserve">Model</t>
@@ -276,7 +273,7 @@
     <t xml:space="preserve">Date created</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-15 20:53:40 MDT</t>
+    <t xml:space="preserve">2026-07-15 21:07:46 MDT</t>
   </si>
   <si>
     <t xml:space="preserve">Package: mysterycall</t>
@@ -1252,7 +1249,7 @@
     <col min="2" max="2" width="8.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="6.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="6.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="5.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="6.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
@@ -1289,22 +1286,22 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.0042</v>
+        <v>2.9608</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.1537</v>
+        <v>0.1468</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>19.545</v>
+        <v>20.162</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>20.17</v>
+        <v>19.314</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>14.923</v>
+        <v>14.483</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>27.261</v>
+        <v>25.755</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>48</v>
@@ -1315,22 +1312,22 @@
         <v>10</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.0341</v>
+        <v>0.0651</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.1877</v>
+        <v>0.1846</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.182</v>
+        <v>0.353</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1.035</v>
+        <v>1.067</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.716</v>
+        <v>0.743</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.495</v>
+        <v>1.533</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>49</v>
@@ -1341,22 +1338,22 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.2316</v>
+        <v>0.2603</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2892</v>
+        <v>0.2867</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.801</v>
+        <v>0.908</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1.261</v>
+        <v>1.297</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.715</v>
+        <v>0.74</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2.222</v>
+        <v>2.276</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>50</v>
@@ -1367,22 +1364,22 @@
         <v>14</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.8113</v>
+        <v>0.8125</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.3492</v>
+        <v>0.3491</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.323</v>
+        <v>2.327</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>2.251</v>
+        <v>2.254</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1.135</v>
+        <v>1.137</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4.463</v>
+        <v>4.467</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>51</v>
@@ -1393,25 +1390,25 @@
         <v>16</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.1858</v>
+        <v>0.2703</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.3204</v>
+        <v>0.3115</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.58</v>
+        <v>0.867</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1.204</v>
+        <v>1.31</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.643</v>
+        <v>0.712</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2.256</v>
+        <v>2.413</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -1419,25 +1416,25 @@
         <v>18</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.4297</v>
+        <v>0.488</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.2002</v>
+        <v>0.1968</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2.147</v>
+        <v>2.48</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1.537</v>
+        <v>1.629</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1.038</v>
+        <v>1.108</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2.275</v>
+        <v>2.396</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -1445,25 +1442,25 @@
         <v>20</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.4351</v>
+        <v>0.4485</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.2805</v>
+        <v>0.2791</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.551</v>
+        <v>1.607</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.545</v>
+        <v>1.566</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.892</v>
+        <v>0.906</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2.678</v>
+        <v>2.706</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -1471,25 +1468,25 @@
         <v>22</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.1525</v>
+        <v>0.2061</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.3334</v>
+        <v>0.3279</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.458</v>
+        <v>0.629</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1.165</v>
+        <v>1.229</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.606</v>
+        <v>0.646</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2.239</v>
+        <v>2.337</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -1497,25 +1494,25 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-0.0514</v>
+        <v>-0.0589</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.08</v>
+        <v>0.0722</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.643</v>
+        <v>-0.816</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.95</v>
+        <v>0.943</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.812</v>
+        <v>0.818</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.111</v>
+        <v>1.086</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -1523,25 +1520,25 @@
         <v>26</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>-0.0423</v>
+        <v>-0.059</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.0694</v>
+        <v>0.0649</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-0.609</v>
+        <v>-0.909</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.959</v>
+        <v>0.943</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.837</v>
+        <v>0.83</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1.098</v>
+        <v>1.071</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -1549,25 +1546,25 @@
         <v>28</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-0.0502</v>
+        <v>-0.0403</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.0617</v>
+        <v>0.06</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.813</v>
+        <v>-0.671</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.951</v>
+        <v>0.961</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.843</v>
+        <v>0.854</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.073</v>
+        <v>1.08</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -1575,25 +1572,25 @@
         <v>30</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-0.0153</v>
+        <v>-0.0224</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.0676</v>
+        <v>0.0648</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.227</v>
+        <v>-0.346</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.985</v>
+        <v>0.978</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.862</v>
+        <v>0.861</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.124</v>
+        <v>1.11</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
@@ -1601,25 +1598,25 @@
         <v>32</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.0825</v>
+        <v>0.1542</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.1375</v>
+        <v>0.1318</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.6</v>
+        <v>1.17</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1.086</v>
+        <v>1.167</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.829</v>
+        <v>0.901</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1.422</v>
+        <v>1.511</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -1627,25 +1624,25 @@
         <v>34</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>-0.1982</v>
+        <v>-0.1988</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.1675</v>
+        <v>0.1639</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-1.183</v>
+        <v>-1.212</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>0.82</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.591</v>
+        <v>0.594</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1.139</v>
+        <v>1.13</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -1653,25 +1650,25 @@
         <v>36</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.491</v>
+        <v>-0.4806</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1955</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-2.455</v>
+        <v>-2.459</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.612</v>
+        <v>0.618</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.414</v>
+        <v>0.422</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.906</v>
+        <v>0.907</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
@@ -1679,25 +1676,25 @@
         <v>38</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>-0.0012</v>
+        <v>-0.1067</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.1729</v>
+        <v>0.1693</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>-0.007</v>
+        <v>-0.631</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.999</v>
+        <v>0.899</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.712</v>
+        <v>0.645</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.402</v>
+        <v>1.252</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -1705,25 +1702,25 @@
         <v>40</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0</v>
+        <v>-0.0221</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.1777</v>
+        <v>0.1738</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>-0.127</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
+        <v>0.978</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.706</v>
+        <v>0.696</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.417</v>
+        <v>1.375</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -1731,25 +1728,25 @@
         <v>42</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>-0.3078</v>
+        <v>-0.4172</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.5366</v>
+        <v>0.5334</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.574</v>
+        <v>-0.782</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.735</v>
+        <v>0.659</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.257</v>
+        <v>0.232</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>2.104</v>
+        <v>1.874</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1757,25 +1754,25 @@
         <v>44</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.1507</v>
+        <v>-0.1245</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1706</v>
+        <v>0.167</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-0.883</v>
+        <v>-0.746</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.86</v>
+        <v>0.883</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.616</v>
+        <v>0.636</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.202</v>
+        <v>1.225</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1800,30 +1797,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>989.28</v>
@@ -1846,22 +1843,22 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>3570.64</v>
+        <v>3534.73</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>3655.98</v>
+        <v>3620.02</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2581.36</v>
+        <v>2545.45</v>
       </c>
       <c r="G3" s="7" t="b">
         <v>0</v>
@@ -1887,24 +1884,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>731</v>
@@ -1921,13 +1918,13 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>0</v>
@@ -1953,90 +1950,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/model_output/supp/supplemental_bundle.xlsx
+++ b/model_output/supp/supplemental_bundle.xlsx
@@ -273,13 +273,13 @@
     <t xml:space="preserve">Date created</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-15 21:07:46 MDT</t>
+    <t xml:space="preserve">2026-07-16 21:58:37 MDT</t>
   </si>
   <si>
     <t xml:space="preserve">Package: mysterycall</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6.0.9006</t>
+    <t xml:space="preserve">1.6.0.9010</t>
   </si>
   <si>
     <t xml:space="preserve">Package: openxlsx</t>

--- a/model_output/supp/supplemental_bundle.xlsx
+++ b/model_output/supp/supplemental_bundle.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t xml:space="preserve">Term</t>
   </si>
@@ -45,117 +45,117 @@
     <t xml:space="preserve">(Intercept)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279</t>
+    <t xml:space="preserve">0.211</t>
   </si>
   <si>
     <t xml:space="preserve">ent_typeFacial Plastics</t>
   </si>
   <si>
-    <t xml:space="preserve">0.706</t>
+    <t xml:space="preserve">0.995</t>
   </si>
   <si>
     <t xml:space="preserve">ent_typeHead and Neck Cancer</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669</t>
+    <t xml:space="preserve">0.650</t>
   </si>
   <si>
     <t xml:space="preserve">ent_typeLaryngology</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386</t>
+    <t xml:space="preserve">0.357</t>
   </si>
   <si>
     <t xml:space="preserve">ent_typeOtology/neurotology</t>
   </si>
   <si>
-    <t xml:space="preserve">0.072</t>
+    <t xml:space="preserve">0.167</t>
   </si>
   <si>
     <t xml:space="preserve">ent_typePediatrics</t>
   </si>
   <si>
-    <t xml:space="preserve">0.031</t>
+    <t xml:space="preserve">0.028</t>
   </si>
   <si>
     <t xml:space="preserve">ent_typeRhinology</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174</t>
+    <t xml:space="preserve">0.151</t>
   </si>
   <si>
     <t xml:space="preserve">ent_typeSleep</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373</t>
+    <t xml:space="preserve">0.344</t>
   </si>
   <si>
     <t xml:space="preserve">ent_per_100k_z</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552</t>
+    <t xml:space="preserve">0.617</t>
   </si>
   <si>
     <t xml:space="preserve">medicaid_fee_index_z</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254</t>
+    <t xml:space="preserve">0.191</t>
   </si>
   <si>
     <t xml:space="preserve">svi_overall_z</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583</t>
+    <t xml:space="preserve">0.425</t>
   </si>
   <si>
     <t xml:space="preserve">dual_pct_z</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958</t>
+    <t xml:space="preserve">0.816</t>
   </si>
   <si>
     <t xml:space="preserve">ruralRural</t>
   </si>
   <si>
-    <t xml:space="preserve">0.922</t>
+    <t xml:space="preserve">0.830</t>
   </si>
   <si>
     <t xml:space="preserve">caller_fDeol</t>
   </si>
   <si>
+    <t xml:space="preserve">0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caller_fFalk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caller_fGregg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caller_fKim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caller_fOther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caller_fWalsh</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt; 0.001</t>
   </si>
   <si>
-    <t xml:space="preserve">caller_fFalk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">caller_fGregg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">caller_fKim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">caller_fOther</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">caller_fWalsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001</t>
-  </si>
-  <si>
     <t xml:space="preserve">Log-Rate</t>
   </si>
   <si>
@@ -165,55 +165,49 @@
     <t xml:space="preserve">&lt;0.001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.364</t>
+    <t xml:space="preserve">0.743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369</t>
   </si>
   <si>
     <t xml:space="preserve">0.020</t>
   </si>
   <si>
-    <t xml:space="preserve">0.013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.014</t>
+    <t xml:space="preserve">0.377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258</t>
   </si>
   <si>
     <t xml:space="preserve">0.528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456</t>
+    <t xml:space="preserve">0.896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465</t>
   </si>
   <si>
     <t xml:space="preserve">Model</t>
@@ -273,13 +267,13 @@
     <t xml:space="preserve">Date created</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-16 21:58:37 MDT</t>
+    <t xml:space="preserve">2026-07-18 12:28:25 MDT</t>
   </si>
   <si>
     <t xml:space="preserve">Package: mysterycall</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6.0.9010</t>
+    <t xml:space="preserve">1.6.1.9002</t>
   </si>
   <si>
     <t xml:space="preserve">Package: openxlsx</t>
@@ -745,22 +739,22 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.2048</v>
+        <v>-0.2383</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.1892</v>
+        <v>0.1907</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-1.082</v>
+        <v>-1.25</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.815</v>
+        <v>0.788</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.562</v>
+        <v>0.542</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.181</v>
+        <v>1.145</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>9</v>
@@ -771,22 +765,22 @@
         <v>10</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>-0.1004</v>
+        <v>0.0018</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.2656</v>
+        <v>0.2676</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>-0.378</v>
+        <v>0.007</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0.905</v>
+        <v>1.002</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.537</v>
+        <v>0.593</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.522</v>
+        <v>1.693</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>11</v>
@@ -797,22 +791,22 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1818</v>
+        <v>-0.1937</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.4256</v>
+        <v>0.4268</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.427</v>
+        <v>-0.454</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.834</v>
+        <v>0.824</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.362</v>
+        <v>0.357</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.92</v>
+        <v>1.902</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>13</v>
@@ -823,22 +817,22 @@
         <v>14</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.5528</v>
+        <v>0.5895</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.6381</v>
+        <v>0.6401</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.866</v>
+        <v>0.921</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1.738</v>
+        <v>1.803</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.498</v>
+        <v>0.514</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6.071</v>
+        <v>6.322</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>15</v>
@@ -849,22 +843,22 @@
         <v>16</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-0.709</v>
+        <v>-0.5441</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.3945</v>
+        <v>0.3934</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-1.797</v>
+        <v>-1.383</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.492</v>
+        <v>0.58</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.227</v>
+        <v>0.268</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.066</v>
+        <v>1.255</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>17</v>
@@ -875,22 +869,22 @@
         <v>18</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.8181</v>
+        <v>0.8289</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.3785</v>
+        <v>0.3778</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2.162</v>
+        <v>2.194</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2.266</v>
+        <v>2.291</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1.079</v>
+        <v>1.093</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>4.758</v>
+        <v>4.804</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>19</v>
@@ -901,22 +895,22 @@
         <v>20</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.7463</v>
+        <v>0.7922</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.5489</v>
+        <v>0.5511</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.36</v>
+        <v>1.437</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2.109</v>
+        <v>2.208</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.719</v>
+        <v>0.75</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>6.185</v>
+        <v>6.503</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>21</v>
@@ -927,22 +921,22 @@
         <v>22</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.5042</v>
+        <v>0.5375</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.5654</v>
+        <v>0.5678</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.892</v>
+        <v>0.947</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1.656</v>
+        <v>1.712</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.547</v>
+        <v>0.562</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5.015</v>
+        <v>5.21</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>23</v>
@@ -953,22 +947,22 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-0.0494</v>
+        <v>-0.042</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.0832</v>
+        <v>0.0841</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.594</v>
+        <v>-0.5</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.952</v>
+        <v>0.959</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.808</v>
+        <v>0.813</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.12</v>
+        <v>1.131</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>25</v>
@@ -979,22 +973,22 @@
         <v>26</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>-0.0941</v>
+        <v>-0.1086</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.0825</v>
+        <v>0.083</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-1.142</v>
+        <v>-1.308</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.91</v>
+        <v>0.897</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.774</v>
+        <v>0.762</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1.07</v>
+        <v>1.056</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>27</v>
@@ -1005,22 +999,22 @@
         <v>28</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-0.0488</v>
+        <v>-0.0712</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.0889</v>
+        <v>0.0894</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.549</v>
+        <v>-0.797</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.952</v>
+        <v>0.931</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8</v>
+        <v>0.782</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.134</v>
+        <v>1.11</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>29</v>
@@ -1031,22 +1025,22 @@
         <v>30</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-0.0049</v>
+        <v>-0.0217</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.0923</v>
+        <v>0.0932</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.053</v>
+        <v>-0.233</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.995</v>
+        <v>0.979</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.83</v>
+        <v>0.815</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.192</v>
+        <v>1.175</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>31</v>
@@ -1057,22 +1051,22 @@
         <v>32</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.0178</v>
+        <v>0.0393</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.1822</v>
+        <v>0.1834</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.098</v>
+        <v>0.214</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1.018</v>
+        <v>1.04</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.712</v>
+        <v>0.726</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1.455</v>
+        <v>1.49</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>33</v>
@@ -1083,22 +1077,22 @@
         <v>34</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.8494</v>
+        <v>0.8123</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.2547</v>
+        <v>0.2546</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>3.335</v>
+        <v>3.19</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.338</v>
+        <v>2.253</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.419</v>
+        <v>1.368</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>3.852</v>
+        <v>3.711</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>35</v>
@@ -1109,22 +1103,22 @@
         <v>36</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.692</v>
+        <v>0.6323</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.2895</v>
+        <v>0.2887</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.391</v>
+        <v>2.19</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.998</v>
+        <v>1.882</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.133</v>
+        <v>1.069</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.523</v>
+        <v>3.314</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>37</v>
@@ -1135,22 +1129,22 @@
         <v>38</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.6378</v>
+        <v>0.6343</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.2543</v>
+        <v>0.2551</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2.508</v>
+        <v>2.487</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.892</v>
+        <v>1.886</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1.15</v>
+        <v>1.144</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>3.115</v>
+        <v>3.109</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>39</v>
@@ -1161,22 +1155,22 @@
         <v>40</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.6849</v>
+        <v>0.7251</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.2545</v>
+        <v>0.2562</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2.691</v>
+        <v>2.83</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1.984</v>
+        <v>2.065</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.204</v>
+        <v>1.25</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3.266</v>
+        <v>3.412</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>41</v>
@@ -1187,22 +1181,22 @@
         <v>42</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>-0.694</v>
+        <v>0.2714</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.6346</v>
+        <v>0.595</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-1.094</v>
+        <v>0.456</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.5</v>
+        <v>1.312</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.144</v>
+        <v>0.409</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1.733</v>
+        <v>4.211</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>43</v>
@@ -1213,22 +1207,22 @@
         <v>44</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.8065</v>
+        <v>0.8418</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.25</v>
+        <v>0.2517</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.226</v>
+        <v>3.344</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.372</v>
+        <v>1.417</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.657</v>
+        <v>3.8</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>45</v>
@@ -1286,22 +1280,22 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2.9608</v>
+        <v>2.9546</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.1468</v>
+        <v>0.1457</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>20.162</v>
+        <v>20.28</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>19.314</v>
+        <v>19.194</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>14.483</v>
+        <v>14.426</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>25.755</v>
+        <v>25.537</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>48</v>
@@ -1312,22 +1306,22 @@
         <v>10</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.0651</v>
+        <v>0.0601</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.1846</v>
+        <v>0.1832</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.353</v>
+        <v>0.328</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1.067</v>
+        <v>1.062</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.533</v>
+        <v>1.521</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>49</v>
@@ -1338,22 +1332,22 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.2603</v>
+        <v>0.2557</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2867</v>
+        <v>0.2846</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.908</v>
+        <v>0.899</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1.297</v>
+        <v>1.291</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2.276</v>
+        <v>2.256</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>50</v>
@@ -1364,22 +1358,22 @@
         <v>14</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.8125</v>
+        <v>0.8045</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.3491</v>
+        <v>0.3462</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.327</v>
+        <v>2.324</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>2.254</v>
+        <v>2.236</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1.137</v>
+        <v>1.134</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4.467</v>
+        <v>4.406</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>51</v>
@@ -1390,25 +1384,25 @@
         <v>16</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2703</v>
+        <v>0.2729</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.3115</v>
+        <v>0.3091</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.867</v>
+        <v>0.883</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1.31</v>
+        <v>1.314</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.712</v>
+        <v>0.717</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2.413</v>
+        <v>2.408</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -1416,25 +1410,25 @@
         <v>18</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.488</v>
+        <v>0.4853</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.1968</v>
+        <v>0.1952</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2.48</v>
+        <v>2.486</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1.629</v>
+        <v>1.625</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>1.108</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2.396</v>
+        <v>2.382</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -1442,22 +1436,22 @@
         <v>20</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.4485</v>
+        <v>0.4424</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.2791</v>
+        <v>0.2769</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.607</v>
+        <v>1.598</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.566</v>
+        <v>1.557</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.906</v>
+        <v>0.905</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2.706</v>
+        <v>2.678</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>53</v>
@@ -1468,22 +1462,22 @@
         <v>22</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.2061</v>
+        <v>0.1938</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.3279</v>
+        <v>0.3253</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.629</v>
+        <v>0.596</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1.229</v>
+        <v>1.214</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.646</v>
+        <v>0.642</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2.337</v>
+        <v>2.296</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>54</v>
@@ -1494,22 +1488,22 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-0.0589</v>
+        <v>-0.0615</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.0722</v>
+        <v>0.0716</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.816</v>
+        <v>-0.858</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.943</v>
+        <v>0.94</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.818</v>
+        <v>0.817</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.086</v>
+        <v>1.082</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>55</v>
@@ -1520,22 +1514,22 @@
         <v>26</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>-0.059</v>
+        <v>-0.0645</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.0649</v>
+        <v>0.0645</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-0.909</v>
+        <v>-1</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.943</v>
+        <v>0.938</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.83</v>
+        <v>0.826</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1.071</v>
+        <v>1.064</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>56</v>
@@ -1546,22 +1540,22 @@
         <v>28</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-0.0403</v>
+        <v>-0.0413</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.06</v>
+        <v>0.0597</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.671</v>
+        <v>-0.691</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.961</v>
+        <v>0.96</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0.854</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.08</v>
+        <v>1.079</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>57</v>
@@ -1572,22 +1566,22 @@
         <v>30</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-0.0224</v>
+        <v>-0.0137</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.0648</v>
+        <v>0.0645</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.346</v>
+        <v>-0.212</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.978</v>
+        <v>0.986</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.861</v>
+        <v>0.869</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.11</v>
+        <v>1.119</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>58</v>
@@ -1598,25 +1592,25 @@
         <v>32</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.1542</v>
+        <v>0.1714</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.1318</v>
+        <v>0.131</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1.17</v>
+        <v>1.308</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1.167</v>
+        <v>1.187</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.901</v>
+        <v>0.918</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1.511</v>
+        <v>1.534</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -1624,25 +1618,25 @@
         <v>34</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>-0.1988</v>
+        <v>-0.1845</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.1639</v>
+        <v>0.163</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-1.212</v>
+        <v>-1.132</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.82</v>
+        <v>0.832</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.594</v>
+        <v>0.604</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1.13</v>
+        <v>1.145</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
@@ -1650,25 +1644,25 @@
         <v>36</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.4806</v>
+        <v>-0.4523</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.1955</v>
+        <v>0.1949</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-2.459</v>
+        <v>-2.32</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.618</v>
+        <v>0.636</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.422</v>
+        <v>0.434</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.907</v>
+        <v>0.932</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
@@ -1676,25 +1670,25 @@
         <v>38</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>-0.1067</v>
+        <v>-0.1058</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.1693</v>
+        <v>0.1679</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>-0.631</v>
+        <v>-0.63</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.899</v>
+        <v>0.9</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.645</v>
+        <v>0.647</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.252</v>
+        <v>1.25</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -1702,25 +1696,25 @@
         <v>40</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.0221</v>
+        <v>-0.0225</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.1738</v>
+        <v>0.1724</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-0.127</v>
+        <v>-0.13</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>0.978</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.696</v>
+        <v>0.697</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.375</v>
+        <v>1.371</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -1728,25 +1722,25 @@
         <v>42</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>-0.4172</v>
+        <v>-0.4124</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.5334</v>
+        <v>0.5291</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.782</v>
+        <v>-0.779</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.232</v>
+        <v>0.235</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1.874</v>
+        <v>1.868</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -1754,25 +1748,25 @@
         <v>44</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.1245</v>
+        <v>-0.1216</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.167</v>
+        <v>0.1663</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-0.746</v>
+        <v>-0.731</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.883</v>
+        <v>0.885</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.636</v>
+        <v>0.639</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.225</v>
+        <v>1.227</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1797,36 +1791,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>989.28</v>
+        <v>991.41</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1081.17</v>
+        <v>1083.3</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>731</v>
@@ -1843,22 +1837,22 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>3534.73</v>
+        <v>3514.64</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>3620.02</v>
+        <v>3599.78</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2545.45</v>
+        <v>2523.23</v>
       </c>
       <c r="G3" s="7" t="b">
         <v>0</v>
@@ -1884,24 +1878,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>731</v>
@@ -1918,13 +1912,13 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>0</v>
@@ -1950,90 +1944,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/model_output/supp/supplemental_bundle.xlsx
+++ b/model_output/supp/supplemental_bundle.xlsx
@@ -267,7 +267,7 @@
     <t xml:space="preserve">Date created</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-18 12:28:25 MDT</t>
+    <t xml:space="preserve">2026-07-18 13:20:43 MDT</t>
   </si>
   <si>
     <t xml:space="preserve">Package: mysterycall</t>

--- a/model_output/supp/supplemental_bundle.xlsx
+++ b/model_output/supp/supplemental_bundle.xlsx
@@ -267,13 +267,13 @@
     <t xml:space="preserve">Date created</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-18 13:20:43 MDT</t>
+    <t xml:space="preserve">2026-07-18 14:33:27 MDT</t>
   </si>
   <si>
     <t xml:space="preserve">Package: mysterycall</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6.1.9002</t>
+    <t xml:space="preserve">1.6.1.9004</t>
   </si>
   <si>
     <t xml:space="preserve">Package: openxlsx</t>

--- a/model_output/supp/supplemental_bundle.xlsx
+++ b/model_output/supp/supplemental_bundle.xlsx
@@ -267,13 +267,13 @@
     <t xml:space="preserve">Date created</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-18 14:33:27 MDT</t>
+    <t xml:space="preserve">2026-07-18 17:26:37 MDT</t>
   </si>
   <si>
     <t xml:space="preserve">Package: mysterycall</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6.1.9004</t>
+    <t xml:space="preserve">1.6.1.9006</t>
   </si>
   <si>
     <t xml:space="preserve">Package: openxlsx</t>
